--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>52.28855</v>
+      </c>
+      <c r="C2">
+        <v>94.31327</v>
+      </c>
+      <c r="D2">
+        <v>78.93602</v>
+      </c>
+      <c r="E2">
+        <v>41.94567</v>
+      </c>
+      <c r="F2">
         <v>52.79541</v>
       </c>
-      <c r="C2">
-        <v>52.28855</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>101.2252</v>
       </c>
-      <c r="E2">
-        <v>94.31327</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>104.7709</v>
       </c>
-      <c r="G2">
-        <v>78.93602</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>64.56095999999999</v>
-      </c>
-      <c r="I2">
-        <v>41.94567</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>61.19403</v>
+      </c>
+      <c r="C3">
+        <v>96.12482</v>
+      </c>
+      <c r="D3">
+        <v>79.25015999999999</v>
+      </c>
+      <c r="E3">
+        <v>38.91478</v>
+      </c>
+      <c r="F3">
         <v>61.79105</v>
       </c>
-      <c r="C3">
-        <v>61.19403</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>102.8121</v>
       </c>
-      <c r="E3">
-        <v>96.12482</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>101.2282</v>
       </c>
-      <c r="G3">
-        <v>79.25015999999999</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>54.62716</v>
-      </c>
-      <c r="I3">
-        <v>38.91478</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>51.18425</v>
+      </c>
+      <c r="C4">
+        <v>93.23712999999999</v>
+      </c>
+      <c r="D4">
+        <v>82.88914</v>
+      </c>
+      <c r="E4">
+        <v>53.46332</v>
+      </c>
+      <c r="F4">
         <v>52.41464</v>
       </c>
-      <c r="C4">
-        <v>51.18425</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>97.50162</v>
       </c>
-      <c r="E4">
-        <v>93.23712999999999</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>102.781</v>
       </c>
-      <c r="G4">
-        <v>82.88914</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>71.10492000000001</v>
-      </c>
-      <c r="I4">
-        <v>53.46332</v>
       </c>
     </row>
     <row r="5">
@@ -504,25 +504,25 @@
         <v>72.30768999999999</v>
       </c>
       <c r="C5">
+        <v>92.22221999999999</v>
+      </c>
+      <c r="D5">
+        <v>78.78788</v>
+      </c>
+      <c r="E5">
+        <v>50.74627</v>
+      </c>
+      <c r="F5">
         <v>72.30768999999999</v>
       </c>
-      <c r="D5">
+      <c r="G5">
         <v>98.88889</v>
       </c>
-      <c r="E5">
-        <v>92.22221999999999</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>93.93939</v>
       </c>
-      <c r="G5">
-        <v>78.78788</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>64.17910999999999</v>
-      </c>
-      <c r="I5">
-        <v>50.74627</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>62.91013</v>
+      </c>
+      <c r="C6">
+        <v>95.0163</v>
+      </c>
+      <c r="D6">
+        <v>77.25948</v>
+      </c>
+      <c r="E6">
+        <v>37.53337</v>
+      </c>
+      <c r="F6">
         <v>63.05278</v>
       </c>
-      <c r="C6">
-        <v>62.91013</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>102.0494</v>
       </c>
-      <c r="E6">
-        <v>95.0163</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>99.02818000000001</v>
       </c>
-      <c r="G6">
-        <v>77.25948</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>51.94875</v>
-      </c>
-      <c r="I6">
-        <v>37.53337</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>55.37118</v>
+      </c>
+      <c r="C7">
+        <v>94.959</v>
+      </c>
+      <c r="D7">
+        <v>75.76633</v>
+      </c>
+      <c r="E7">
+        <v>37.87879</v>
+      </c>
+      <c r="F7">
         <v>55.76419</v>
       </c>
-      <c r="C7">
-        <v>55.37118</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>102.4901</v>
       </c>
-      <c r="E7">
-        <v>94.959</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>98.49624</v>
       </c>
-      <c r="G7">
-        <v>75.76633</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>53.33952</v>
-      </c>
-      <c r="I7">
-        <v>37.87879</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>52.76166</v>
+      </c>
+      <c r="C8">
+        <v>94.53386999999999</v>
+      </c>
+      <c r="D8">
+        <v>81.21805999999999</v>
+      </c>
+      <c r="E8">
+        <v>46.98514</v>
+      </c>
+      <c r="F8">
         <v>53.69278</v>
       </c>
-      <c r="C8">
-        <v>52.76166</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>100.0066</v>
       </c>
-      <c r="E8">
-        <v>94.53386999999999</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>103.8718</v>
       </c>
-      <c r="G8">
-        <v>81.21805999999999</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>70.41869</v>
-      </c>
-      <c r="I8">
-        <v>46.98514</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>50.63776</v>
+      </c>
+      <c r="C9">
+        <v>95.44492</v>
+      </c>
+      <c r="D9">
+        <v>77.24138000000001</v>
+      </c>
+      <c r="E9">
+        <v>29.62963</v>
+      </c>
+      <c r="F9">
         <v>51.14796</v>
       </c>
-      <c r="C9">
-        <v>50.63776</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>101.6949</v>
       </c>
-      <c r="E9">
-        <v>95.44492</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>93.33334000000001</v>
       </c>
-      <c r="G9">
-        <v>77.24138000000001</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>45.28077</v>
-      </c>
-      <c r="I9">
-        <v>29.62963</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>54.96214</v>
+      </c>
+      <c r="C10">
+        <v>95.53951000000001</v>
+      </c>
+      <c r="D10">
+        <v>83.62416</v>
+      </c>
+      <c r="E10">
+        <v>39.97334</v>
+      </c>
+      <c r="F10">
         <v>55.44041</v>
       </c>
-      <c r="C10">
-        <v>54.96214</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>101.8975</v>
       </c>
-      <c r="E10">
-        <v>95.53951000000001</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>106.7919</v>
       </c>
-      <c r="G10">
-        <v>83.62416</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>60.38667</v>
-      </c>
-      <c r="I10">
-        <v>39.97334</v>
       </c>
     </row>
     <row r="11">
@@ -687,28 +687,28 @@
         </is>
       </c>
       <c r="B11">
+        <v>52.90791</v>
+      </c>
+      <c r="C11">
+        <v>96.00221999999999</v>
+      </c>
+      <c r="D11">
+        <v>83.25301</v>
+      </c>
+      <c r="E11">
+        <v>35.43523</v>
+      </c>
+      <c r="F11">
         <v>53.06947</v>
       </c>
-      <c r="C11">
-        <v>52.90791</v>
-      </c>
-      <c r="D11">
+      <c r="G11">
         <v>100.8329</v>
       </c>
-      <c r="E11">
-        <v>96.00221999999999</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>104.9398</v>
       </c>
-      <c r="G11">
-        <v>83.25301</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>53.73544</v>
-      </c>
-      <c r="I11">
-        <v>35.43523</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>58.7822</v>
+      </c>
+      <c r="C12">
+        <v>96.02184</v>
+      </c>
+      <c r="D12">
+        <v>82.56579000000001</v>
+      </c>
+      <c r="E12">
+        <v>41.56415</v>
+      </c>
+      <c r="F12">
         <v>59.60188</v>
       </c>
-      <c r="C12">
-        <v>58.7822</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>101.4821</v>
       </c>
-      <c r="E12">
-        <v>96.02184</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>107.5658</v>
       </c>
-      <c r="G12">
-        <v>82.56579000000001</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>58.78735</v>
-      </c>
-      <c r="I12">
-        <v>41.56415</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>55.55556</v>
+      </c>
+      <c r="C13">
+        <v>96.30486000000001</v>
+      </c>
+      <c r="D13">
+        <v>86.71726</v>
+      </c>
+      <c r="E13">
+        <v>37.72947</v>
+      </c>
+      <c r="F13">
         <v>56.04782</v>
       </c>
-      <c r="C13">
-        <v>55.55556</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>100.97</v>
       </c>
-      <c r="E13">
-        <v>96.30486000000001</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>109.0133</v>
       </c>
-      <c r="G13">
-        <v>86.71726</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>53.71981</v>
-      </c>
-      <c r="I13">
-        <v>37.72947</v>
       </c>
     </row>
     <row r="14">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>57.89066</v>
+      </c>
+      <c r="C14">
+        <v>96.96249</v>
+      </c>
+      <c r="D14">
+        <v>87.08062</v>
+      </c>
+      <c r="E14">
+        <v>38.85445</v>
+      </c>
+      <c r="F14">
         <v>58.1233</v>
       </c>
-      <c r="C14">
-        <v>57.89066</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>99.89435</v>
       </c>
-      <c r="E14">
-        <v>96.96249</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>104.0561</v>
       </c>
-      <c r="G14">
-        <v>87.08062</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>53.85569</v>
-      </c>
-      <c r="I14">
-        <v>38.85445</v>
       </c>
     </row>
     <row r="15">
@@ -811,28 +811,28 @@
         </is>
       </c>
       <c r="B15">
+        <v>54.74026</v>
+      </c>
+      <c r="C15">
+        <v>97.0025</v>
+      </c>
+      <c r="D15">
+        <v>86.09975</v>
+      </c>
+      <c r="E15">
+        <v>35.96741</v>
+      </c>
+      <c r="F15">
         <v>55.19481</v>
       </c>
-      <c r="C15">
-        <v>54.74026</v>
-      </c>
-      <c r="D15">
+      <c r="G15">
         <v>100.791</v>
       </c>
-      <c r="E15">
-        <v>97.0025</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>108.0131</v>
       </c>
-      <c r="G15">
-        <v>86.09975</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>48.14664</v>
-      </c>
-      <c r="I15">
-        <v>35.96741</v>
       </c>
     </row>
     <row r="16">
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="B16">
+        <v>63.51351</v>
+      </c>
+      <c r="C16">
+        <v>94.91833</v>
+      </c>
+      <c r="D16">
+        <v>82.37179999999999</v>
+      </c>
+      <c r="E16">
+        <v>38.50837</v>
+      </c>
+      <c r="F16">
         <v>64.5946</v>
       </c>
-      <c r="C16">
-        <v>63.51351</v>
-      </c>
-      <c r="D16">
+      <c r="G16">
         <v>101.0889</v>
       </c>
-      <c r="E16">
-        <v>94.91833</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>97.75641</v>
       </c>
-      <c r="G16">
-        <v>82.37179999999999</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>47.33638</v>
-      </c>
-      <c r="I16">
-        <v>38.50837</v>
       </c>
     </row>
     <row r="17">
@@ -876,25 +876,25 @@
         <v>59.46792</v>
       </c>
       <c r="C17">
+        <v>97.00483</v>
+      </c>
+      <c r="D17">
+        <v>88.17829</v>
+      </c>
+      <c r="E17">
+        <v>35.57789</v>
+      </c>
+      <c r="F17">
         <v>59.46792</v>
       </c>
-      <c r="D17">
+      <c r="G17">
         <v>100.5797</v>
       </c>
-      <c r="E17">
-        <v>97.00483</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>97.09303</v>
       </c>
-      <c r="G17">
-        <v>88.17829</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>48.74372</v>
-      </c>
-      <c r="I17">
-        <v>35.57789</v>
       </c>
     </row>
     <row r="18">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>61.31387</v>
+      </c>
+      <c r="C18">
+        <v>94.56682000000001</v>
+      </c>
+      <c r="D18">
+        <v>85.60794</v>
+      </c>
+      <c r="E18">
+        <v>40.15748</v>
+      </c>
+      <c r="F18">
         <v>61.86131</v>
       </c>
-      <c r="C18">
-        <v>61.31387</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>98.82526</v>
       </c>
-      <c r="E18">
-        <v>94.56682000000001</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>99.25557999999999</v>
       </c>
-      <c r="G18">
-        <v>85.60794</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>53.88076</v>
-      </c>
-      <c r="I18">
-        <v>40.15748</v>
       </c>
     </row>
     <row r="19">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>61.50825</v>
+      </c>
+      <c r="C19">
+        <v>95.88824</v>
+      </c>
+      <c r="D19">
+        <v>78.5003</v>
+      </c>
+      <c r="E19">
+        <v>42.28155</v>
+      </c>
+      <c r="F19">
         <v>61.8696</v>
       </c>
-      <c r="C19">
-        <v>61.50825</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>102.8044</v>
       </c>
-      <c r="E19">
-        <v>95.88824</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>103.1439</v>
       </c>
-      <c r="G19">
-        <v>78.5003</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>63.13664</v>
-      </c>
-      <c r="I19">
-        <v>42.28155</v>
       </c>
     </row>
     <row r="20">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>63.00639</v>
+      </c>
+      <c r="C20">
+        <v>96.03188</v>
+      </c>
+      <c r="D20">
+        <v>80.56238999999999</v>
+      </c>
+      <c r="E20">
+        <v>39.15975</v>
+      </c>
+      <c r="F20">
         <v>63.21962</v>
       </c>
-      <c r="C20">
-        <v>63.00639</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>102.0903</v>
       </c>
-      <c r="E20">
-        <v>96.03188</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>107.4517</v>
       </c>
-      <c r="G20">
-        <v>80.56238999999999</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>55.41148</v>
-      </c>
-      <c r="I20">
-        <v>39.15975</v>
       </c>
     </row>
     <row r="21">
@@ -997,28 +997,28 @@
         </is>
       </c>
       <c r="B21">
+        <v>60.85106</v>
+      </c>
+      <c r="C21">
+        <v>95.73643</v>
+      </c>
+      <c r="D21">
+        <v>80.23679</v>
+      </c>
+      <c r="E21">
+        <v>35.67913</v>
+      </c>
+      <c r="F21">
         <v>61.06383</v>
       </c>
-      <c r="C21">
-        <v>60.85106</v>
-      </c>
-      <c r="D21">
+      <c r="G21">
         <v>102.0349</v>
       </c>
-      <c r="E21">
-        <v>95.73643</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>100.1822</v>
       </c>
-      <c r="G21">
-        <v>80.23679</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>47.98228</v>
-      </c>
-      <c r="I21">
-        <v>35.67913</v>
       </c>
     </row>
     <row r="22">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="B22">
+        <v>56.06147</v>
+      </c>
+      <c r="C22">
+        <v>96.26572</v>
+      </c>
+      <c r="D22">
+        <v>85.12658999999999</v>
+      </c>
+      <c r="E22">
+        <v>49.88844</v>
+      </c>
+      <c r="F22">
         <v>56.40296</v>
       </c>
-      <c r="C22">
-        <v>56.06147</v>
-      </c>
-      <c r="D22">
+      <c r="G22">
         <v>100.6682</v>
       </c>
-      <c r="E22">
-        <v>96.26572</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>104.6677</v>
       </c>
-      <c r="G22">
-        <v>85.12658999999999</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>73.22624</v>
-      </c>
-      <c r="I22">
-        <v>49.88844</v>
       </c>
     </row>
     <row r="23">
@@ -1062,25 +1062,25 @@
         <v>59.88334</v>
       </c>
       <c r="C23">
+        <v>96.95325</v>
+      </c>
+      <c r="D23">
+        <v>82.34363</v>
+      </c>
+      <c r="E23">
+        <v>37.99688</v>
+      </c>
+      <c r="F23">
         <v>59.88334</v>
       </c>
-      <c r="D23">
+      <c r="G23">
         <v>103.172</v>
       </c>
-      <c r="E23">
-        <v>96.95325</v>
-      </c>
-      <c r="F23">
+      <c r="H23">
         <v>104.3547</v>
       </c>
-      <c r="G23">
-        <v>82.34363</v>
-      </c>
-      <c r="H23">
+      <c r="I23">
         <v>50.5456</v>
-      </c>
-      <c r="I23">
-        <v>37.99688</v>
       </c>
     </row>
     <row r="24">
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B24">
+        <v>58.46612</v>
+      </c>
+      <c r="C24">
+        <v>95.49464</v>
+      </c>
+      <c r="D24">
+        <v>80.59645</v>
+      </c>
+      <c r="E24">
+        <v>37.53527</v>
+      </c>
+      <c r="F24">
         <v>58.92777</v>
       </c>
-      <c r="C24">
-        <v>58.46612</v>
-      </c>
-      <c r="D24">
+      <c r="G24">
         <v>101.6908</v>
       </c>
-      <c r="E24">
-        <v>95.49464</v>
-      </c>
-      <c r="F24">
+      <c r="H24">
         <v>102.8501</v>
       </c>
-      <c r="G24">
-        <v>80.59645</v>
-      </c>
-      <c r="H24">
+      <c r="I24">
         <v>53.37566</v>
-      </c>
-      <c r="I24">
-        <v>37.53527</v>
       </c>
     </row>
     <row r="25">
@@ -1121,28 +1121,28 @@
         </is>
       </c>
       <c r="B25">
+        <v>48.90873</v>
+      </c>
+      <c r="C25">
+        <v>94.21129000000001</v>
+      </c>
+      <c r="D25">
+        <v>80.60109</v>
+      </c>
+      <c r="E25">
+        <v>40.3307</v>
+      </c>
+      <c r="F25">
         <v>49.40476</v>
       </c>
-      <c r="C25">
-        <v>48.90873</v>
-      </c>
-      <c r="D25">
+      <c r="G25">
         <v>99.71056</v>
       </c>
-      <c r="E25">
-        <v>94.21129000000001</v>
-      </c>
-      <c r="F25">
+      <c r="H25">
         <v>100.1366</v>
       </c>
-      <c r="G25">
-        <v>80.60109</v>
-      </c>
-      <c r="H25">
+      <c r="I25">
         <v>54.49317</v>
-      </c>
-      <c r="I25">
-        <v>40.3307</v>
       </c>
     </row>
     <row r="26">
@@ -1152,28 +1152,28 @@
         </is>
       </c>
       <c r="B26">
+        <v>58.50092</v>
+      </c>
+      <c r="C26">
+        <v>96.88486</v>
+      </c>
+      <c r="D26">
+        <v>73.96849</v>
+      </c>
+      <c r="E26">
+        <v>33.06773</v>
+      </c>
+      <c r="F26">
         <v>58.68373</v>
       </c>
-      <c r="C26">
-        <v>58.50092</v>
-      </c>
-      <c r="D26">
+      <c r="G26">
         <v>104.5741</v>
       </c>
-      <c r="E26">
-        <v>96.88486</v>
-      </c>
-      <c r="F26">
+      <c r="H26">
         <v>97.5994</v>
       </c>
-      <c r="G26">
-        <v>73.96849</v>
-      </c>
-      <c r="H26">
+      <c r="I26">
         <v>46.48074</v>
-      </c>
-      <c r="I26">
-        <v>33.06773</v>
       </c>
     </row>
     <row r="27">
@@ -1183,28 +1183,28 @@
         </is>
       </c>
       <c r="B27">
+        <v>50.09225</v>
+      </c>
+      <c r="C27">
+        <v>91.67702</v>
+      </c>
+      <c r="D27">
+        <v>78.7234</v>
+      </c>
+      <c r="E27">
+        <v>33.78378</v>
+      </c>
+      <c r="F27">
         <v>50.27675</v>
       </c>
-      <c r="C27">
-        <v>50.09225</v>
-      </c>
-      <c r="D27">
+      <c r="G27">
         <v>95.83851</v>
       </c>
-      <c r="E27">
-        <v>91.67702</v>
-      </c>
-      <c r="F27">
+      <c r="H27">
         <v>99.24906</v>
       </c>
-      <c r="G27">
-        <v>78.7234</v>
-      </c>
-      <c r="H27">
+      <c r="I27">
         <v>47.09459</v>
-      </c>
-      <c r="I27">
-        <v>33.78378</v>
       </c>
     </row>
     <row r="28">
@@ -1214,28 +1214,28 @@
         </is>
       </c>
       <c r="B28">
+        <v>57.95454</v>
+      </c>
+      <c r="C28">
+        <v>93.20844</v>
+      </c>
+      <c r="D28">
+        <v>74.88226</v>
+      </c>
+      <c r="E28">
+        <v>32.74583</v>
+      </c>
+      <c r="F28">
         <v>58.06818</v>
       </c>
-      <c r="C28">
-        <v>57.95454</v>
-      </c>
-      <c r="D28">
+      <c r="G28">
         <v>99.45355000000001</v>
       </c>
-      <c r="E28">
-        <v>93.20844</v>
-      </c>
-      <c r="F28">
+      <c r="H28">
         <v>96.7033</v>
       </c>
-      <c r="G28">
-        <v>74.88226</v>
-      </c>
-      <c r="H28">
+      <c r="I28">
         <v>49.16512</v>
-      </c>
-      <c r="I28">
-        <v>32.74583</v>
       </c>
     </row>
     <row r="29">
@@ -1245,28 +1245,28 @@
         </is>
       </c>
       <c r="B29">
+        <v>60.7721</v>
+      </c>
+      <c r="C29">
+        <v>96.31704999999999</v>
+      </c>
+      <c r="D29">
+        <v>85.46875</v>
+      </c>
+      <c r="E29">
+        <v>44.91593</v>
+      </c>
+      <c r="F29">
         <v>61.39477</v>
       </c>
-      <c r="C29">
-        <v>60.7721</v>
-      </c>
-      <c r="D29">
+      <c r="G29">
         <v>100.4804</v>
       </c>
-      <c r="E29">
-        <v>96.31704999999999</v>
-      </c>
-      <c r="F29">
+      <c r="H29">
         <v>105.3125</v>
       </c>
-      <c r="G29">
-        <v>85.46875</v>
-      </c>
-      <c r="H29">
+      <c r="I29">
         <v>61.64932</v>
-      </c>
-      <c r="I29">
-        <v>44.91593</v>
       </c>
     </row>
     <row r="30">
@@ -1276,28 +1276,28 @@
         </is>
       </c>
       <c r="B30">
+        <v>60.03613</v>
+      </c>
+      <c r="C30">
+        <v>95.63118</v>
+      </c>
+      <c r="D30">
+        <v>82.19859</v>
+      </c>
+      <c r="E30">
+        <v>38.75</v>
+      </c>
+      <c r="F30">
         <v>61.18594</v>
       </c>
-      <c r="C30">
-        <v>60.03613</v>
-      </c>
-      <c r="D30">
+      <c r="G30">
         <v>100.7703</v>
       </c>
-      <c r="E30">
-        <v>95.63118</v>
-      </c>
-      <c r="F30">
+      <c r="H30">
         <v>100.5202</v>
       </c>
-      <c r="G30">
-        <v>82.19859</v>
-      </c>
-      <c r="H30">
+      <c r="I30">
         <v>57.25694</v>
-      </c>
-      <c r="I30">
-        <v>38.75</v>
       </c>
     </row>
     <row r="31">
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="B31">
+        <v>65.3575</v>
+      </c>
+      <c r="C31">
+        <v>96.27967</v>
+      </c>
+      <c r="D31">
+        <v>82.21093</v>
+      </c>
+      <c r="E31">
+        <v>32.83784</v>
+      </c>
+      <c r="F31">
         <v>65.35751</v>
       </c>
-      <c r="C31">
-        <v>65.3575</v>
-      </c>
-      <c r="D31">
+      <c r="G31">
         <v>101.4753</v>
       </c>
-      <c r="E31">
-        <v>96.27967</v>
-      </c>
-      <c r="F31">
+      <c r="H31">
         <v>97.33163999999999</v>
       </c>
-      <c r="G31">
-        <v>82.21093</v>
-      </c>
-      <c r="H31">
+      <c r="I31">
         <v>46.01351</v>
-      </c>
-      <c r="I31">
-        <v>32.83784</v>
       </c>
     </row>
     <row r="32">
@@ -1338,28 +1338,28 @@
         </is>
       </c>
       <c r="B32">
+        <v>64.86225</v>
+      </c>
+      <c r="C32">
+        <v>96.66665999999999</v>
+      </c>
+      <c r="D32">
+        <v>83.2158</v>
+      </c>
+      <c r="E32">
+        <v>38.02657</v>
+      </c>
+      <c r="F32">
         <v>65.05558000000001</v>
       </c>
-      <c r="C32">
-        <v>64.86225</v>
-      </c>
-      <c r="D32">
+      <c r="G32">
         <v>102.6087</v>
       </c>
-      <c r="E32">
-        <v>96.66665999999999</v>
-      </c>
-      <c r="F32">
+      <c r="H32">
         <v>99.64739</v>
       </c>
-      <c r="G32">
-        <v>83.2158</v>
-      </c>
-      <c r="H32">
+      <c r="I32">
         <v>55.82543</v>
-      </c>
-      <c r="I32">
-        <v>38.02657</v>
       </c>
     </row>
     <row r="33">
@@ -1372,25 +1372,25 @@
         <v>66.21392</v>
       </c>
       <c r="C33">
+        <v>96.66665999999999</v>
+      </c>
+      <c r="D33">
+        <v>82.67543999999999</v>
+      </c>
+      <c r="E33">
+        <v>34.85309</v>
+      </c>
+      <c r="F33">
         <v>66.21392</v>
       </c>
-      <c r="D33">
+      <c r="G33">
         <v>102.5</v>
       </c>
-      <c r="E33">
-        <v>96.66665999999999</v>
-      </c>
-      <c r="F33">
+      <c r="H33">
         <v>107.4561</v>
       </c>
-      <c r="G33">
-        <v>82.67543999999999</v>
-      </c>
-      <c r="H33">
+      <c r="I33">
         <v>51.77305</v>
-      </c>
-      <c r="I33">
-        <v>34.85309</v>
       </c>
     </row>
     <row r="34">
@@ -1400,28 +1400,28 @@
         </is>
       </c>
       <c r="B34">
+        <v>60.99349</v>
+      </c>
+      <c r="C34">
+        <v>96.38761</v>
+      </c>
+      <c r="D34">
+        <v>83.19414999999999</v>
+      </c>
+      <c r="E34">
+        <v>37.85097</v>
+      </c>
+      <c r="F34">
         <v>61.48209</v>
       </c>
-      <c r="C34">
-        <v>60.99349</v>
-      </c>
-      <c r="D34">
+      <c r="G34">
         <v>103.6697</v>
       </c>
-      <c r="E34">
-        <v>96.38761</v>
-      </c>
-      <c r="F34">
+      <c r="H34">
         <v>112.1086</v>
       </c>
-      <c r="G34">
-        <v>83.19414999999999</v>
-      </c>
-      <c r="H34">
+      <c r="I34">
         <v>53.23974</v>
-      </c>
-      <c r="I34">
-        <v>37.85097</v>
       </c>
     </row>
     <row r="35">
@@ -1431,28 +1431,28 @@
         </is>
       </c>
       <c r="B35">
+        <v>67.20574999999999</v>
+      </c>
+      <c r="C35">
+        <v>96.58172999999999</v>
+      </c>
+      <c r="D35">
+        <v>82.65682</v>
+      </c>
+      <c r="E35">
+        <v>36.79954</v>
+      </c>
+      <c r="F35">
         <v>68.19407</v>
       </c>
-      <c r="C35">
-        <v>67.20574999999999</v>
-      </c>
-      <c r="D35">
+      <c r="G35">
         <v>102.051</v>
       </c>
-      <c r="E35">
-        <v>96.58172999999999</v>
-      </c>
-      <c r="F35">
+      <c r="H35">
         <v>104.551</v>
       </c>
-      <c r="G35">
-        <v>82.65682</v>
-      </c>
-      <c r="H35">
+      <c r="I35">
         <v>51.58868</v>
-      </c>
-      <c r="I35">
-        <v>36.79954</v>
       </c>
     </row>
     <row r="36">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B36">
+        <v>56.38495</v>
+      </c>
+      <c r="C36">
+        <v>94.91257</v>
+      </c>
+      <c r="D36">
+        <v>81.57217</v>
+      </c>
+      <c r="E36">
+        <v>48.64099</v>
+      </c>
+      <c r="F36">
         <v>56.90279</v>
       </c>
-      <c r="C36">
-        <v>56.38495</v>
-      </c>
-      <c r="D36">
+      <c r="G36">
         <v>100.805</v>
       </c>
-      <c r="E36">
-        <v>94.91257</v>
-      </c>
-      <c r="F36">
+      <c r="H36">
         <v>105.0023</v>
       </c>
-      <c r="G36">
-        <v>81.57217</v>
-      </c>
-      <c r="H36">
+      <c r="I36">
         <v>72.55956</v>
-      </c>
-      <c r="I36">
-        <v>48.64099</v>
       </c>
     </row>
     <row r="37">
@@ -1493,28 +1493,28 @@
         </is>
       </c>
       <c r="B37">
+        <v>55.78171</v>
+      </c>
+      <c r="C37">
+        <v>93.13321999999999</v>
+      </c>
+      <c r="D37">
+        <v>78.87324</v>
+      </c>
+      <c r="E37">
+        <v>39.00415</v>
+      </c>
+      <c r="F37">
         <v>56.10619</v>
       </c>
-      <c r="C37">
-        <v>55.78171</v>
-      </c>
-      <c r="D37">
+      <c r="G37">
         <v>99.71217</v>
       </c>
-      <c r="E37">
-        <v>93.13321999999999</v>
-      </c>
-      <c r="F37">
+      <c r="H37">
         <v>107.1987</v>
       </c>
-      <c r="G37">
-        <v>78.87324</v>
-      </c>
-      <c r="H37">
+      <c r="I37">
         <v>56.49081</v>
-      </c>
-      <c r="I37">
-        <v>39.00415</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1524,28 @@
         </is>
       </c>
       <c r="B38">
+        <v>51.16641</v>
+      </c>
+      <c r="C38">
+        <v>93.87533999999999</v>
+      </c>
+      <c r="D38">
+        <v>79.68254</v>
+      </c>
+      <c r="E38">
+        <v>35.16424</v>
+      </c>
+      <c r="F38">
         <v>51.63297</v>
       </c>
-      <c r="C38">
-        <v>51.16641</v>
-      </c>
-      <c r="D38">
+      <c r="G38">
         <v>99.34959000000001</v>
       </c>
-      <c r="E38">
-        <v>93.87533999999999</v>
-      </c>
-      <c r="F38">
+      <c r="H38">
         <v>106.9841</v>
       </c>
-      <c r="G38">
-        <v>79.68254</v>
-      </c>
-      <c r="H38">
+      <c r="I38">
         <v>49.75768</v>
-      </c>
-      <c r="I38">
-        <v>35.16424</v>
       </c>
     </row>
     <row r="39">
@@ -1555,28 +1555,28 @@
         </is>
       </c>
       <c r="B39">
+        <v>56.35719</v>
+      </c>
+      <c r="C39">
+        <v>94.54418</v>
+      </c>
+      <c r="D39">
+        <v>81.97929999999999</v>
+      </c>
+      <c r="E39">
+        <v>46.77788</v>
+      </c>
+      <c r="F39">
         <v>56.84885</v>
       </c>
-      <c r="C39">
-        <v>56.35719</v>
-      </c>
-      <c r="D39">
+      <c r="G39">
         <v>99.88342</v>
       </c>
-      <c r="E39">
-        <v>94.54418</v>
-      </c>
-      <c r="F39">
+      <c r="H39">
         <v>105.9549</v>
       </c>
-      <c r="G39">
-        <v>81.97929999999999</v>
-      </c>
-      <c r="H39">
+      <c r="I39">
         <v>69.15922999999999</v>
-      </c>
-      <c r="I39">
-        <v>46.77788</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:37</t>
+    <t xml:space="preserve">2026-08-03 09:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03 09:35</t>
+    <t xml:space="preserve">2026-08-05 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:31</t>
+    <t xml:space="preserve">2026-08-05 18:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 18:11</t>
+    <t xml:space="preserve">2026-08-16 09:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:43</t>
+    <t xml:space="preserve">2026-08-19 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:38</t>
+    <t xml:space="preserve">2026-08-28 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:19</t>
+    <t xml:space="preserve">2026-09-06 17:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
